--- a/Demo/SCH-STH/demo_sppa_impact_2511_3_resultat.xlsx
+++ b/Demo/SCH-STH/demo_sppa_impact_2511_3_resultat.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldhealthorg-my.sharepoint.com/personal/yumbad_who_int/Documents/Desktop/to delete/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\SCH-STH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="13_ncr:1_{94D4F217-46AC-47A7-BB1A-DDA5187499DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7CE5B5D-9362-42C0-A608-C51E214056A3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E0EFEC-89D7-470A-93BA-3ED4F1008C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="299">
   <si>
     <t>type</t>
   </si>
@@ -372,9 +372,6 @@
     <t>${r_site_code}</t>
   </si>
   <si>
-    <t>sn_sppa_impact_2510_3_resultat_v3</t>
-  </si>
-  <si>
     <t>bind::db_filter_by_col_6</t>
   </si>
   <si>
@@ -387,9 +384,6 @@
     <t>r_urine_positif</t>
   </si>
   <si>
-    <t>${r_urine_positif} = 'Oui'</t>
-  </si>
-  <si>
     <t>r_autre_parasite</t>
   </si>
   <si>
@@ -414,18 +408,12 @@
     <t>Hymenolepis nana</t>
   </si>
   <si>
-    <t>Anguillule</t>
-  </si>
-  <si>
     <t>Diphyllobothrium latum</t>
   </si>
   <si>
     <t>Isospera belli</t>
   </si>
   <si>
-    <t>Douves </t>
-  </si>
-  <si>
     <t>Giardia.intestinalis</t>
   </si>
   <si>
@@ -501,21 +489,6 @@
     <t>(${r_hymenolepis_sa} + ${r_hymenolepis_sb})*12</t>
   </si>
   <si>
-    <t>selected(${r_autre_parasite_detail}, 'Anguillule')</t>
-  </si>
-  <si>
-    <t>r_anguillule_sa</t>
-  </si>
-  <si>
-    <t>r_anguillule_sb</t>
-  </si>
-  <si>
-    <t>r_anguillule_intensity</t>
-  </si>
-  <si>
-    <t>(${r_anguillule_sa} + ${r_anguillule_sb})*12</t>
-  </si>
-  <si>
     <t>selected(${r_autre_parasite_detail}, 'Diphyllobothrium.latum')</t>
   </si>
   <si>
@@ -546,30 +519,6 @@
     <t>(${r_isospera_sa} + ${r_isospera_sb})*12</t>
   </si>
   <si>
-    <t>Douves</t>
-  </si>
-  <si>
-    <t>selected(${r_autre_parasite_detail}, 'Douves')</t>
-  </si>
-  <si>
-    <t>r_douves_sa</t>
-  </si>
-  <si>
-    <t>r_douves_sb</t>
-  </si>
-  <si>
-    <t>r_douves_intensity</t>
-  </si>
-  <si>
-    <t>(${r_douves_sa} + ${r_douves_sb})*12</t>
-  </si>
-  <si>
-    <t>${r_autre_parasite} = 'Oui'</t>
-  </si>
-  <si>
-    <t>(2025 Oct) - 3. SCH/STH – Resultats</t>
-  </si>
-  <si>
     <t>r_admin1</t>
   </si>
   <si>
@@ -741,9 +690,6 @@
     <t>${r_test} = 'Urine filtration + Kato katz'</t>
   </si>
   <si>
-    <t>${r_test} = 'Urine filtration + Kato katz' and ${r_k_positif} = 'Oui'</t>
-  </si>
-  <si>
     <t>Urine filtration + Kato katz</t>
   </si>
   <si>
@@ -916,6 +862,63 @@
   </si>
   <si>
     <t>${r_id_type} = 'ID_generation'</t>
+  </si>
+  <si>
+    <t>(Demo) - 3. SCH/STH – Resultats</t>
+  </si>
+  <si>
+    <t>col_7</t>
+  </si>
+  <si>
+    <t>sn_sppa_impact_2510_3_resultat</t>
+  </si>
+  <si>
+    <t>${r_urine_positif} = 'Yes'</t>
+  </si>
+  <si>
+    <t>${r_test} = 'Urine filtration + Kato katz' and ${r_k_positif} = 'Yes'</t>
+  </si>
+  <si>
+    <t>${r_autre_parasite} = 'Yes'</t>
+  </si>
+  <si>
+    <t>r_Fluke_sa</t>
+  </si>
+  <si>
+    <t>selected(${r_autre_parasite_detail}, 'Fluke')</t>
+  </si>
+  <si>
+    <t>r_Fluke_sb</t>
+  </si>
+  <si>
+    <t>r_Fluke_intensity</t>
+  </si>
+  <si>
+    <t>(${r_Fluke_sa} + ${r_Fluke_sb})*12</t>
+  </si>
+  <si>
+    <t>Fluke</t>
+  </si>
+  <si>
+    <t>Fluke </t>
+  </si>
+  <si>
+    <t>r_Eel_sa</t>
+  </si>
+  <si>
+    <t>selected(${r_autre_parasite_detail}, 'Eel')</t>
+  </si>
+  <si>
+    <t>r_Eel_sb</t>
+  </si>
+  <si>
+    <t>r_Eel_intensity</t>
+  </si>
+  <si>
+    <t>(${r_Eel_sa} + ${r_Eel_sb})*12</t>
+  </si>
+  <si>
+    <t>Eel</t>
   </si>
 </sst>
 </file>
@@ -1622,10 +1625,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>2</v>
@@ -1634,7 +1637,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>4</v>
@@ -1676,7 +1679,7 @@
         <v>104</v>
       </c>
       <c r="U1" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="3" customFormat="1" ht="31.5">
@@ -1714,16 +1717,17 @@
       <c r="R2" s="11"/>
       <c r="S2" s="11"/>
       <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
     </row>
     <row r="3" spans="1:21" s="3" customFormat="1">
       <c r="A3" s="23" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="D3" s="37"/>
       <c r="E3" s="6"/>
@@ -1746,6 +1750,7 @@
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
       <c r="T3" s="11"/>
+      <c r="U3" s="11"/>
     </row>
     <row r="4" spans="1:21" s="26" customFormat="1">
       <c r="A4" s="23" t="s">
@@ -1755,7 +1760,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="48" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="D4" s="48"/>
       <c r="E4" s="23"/>
@@ -1774,12 +1779,13 @@
         <v>106</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="Q4" s="23"/>
       <c r="R4" s="23"/>
       <c r="S4" s="23"/>
       <c r="T4" s="23"/>
+      <c r="U4" s="23"/>
     </row>
     <row r="5" spans="1:21" s="26" customFormat="1">
       <c r="A5" s="23" t="s">
@@ -1789,7 +1795,7 @@
         <v>33</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="D5" s="48"/>
       <c r="E5" s="23"/>
@@ -1814,16 +1820,17 @@
       <c r="R5" s="23"/>
       <c r="S5" s="23"/>
       <c r="T5" s="23"/>
+      <c r="U5" s="23"/>
     </row>
     <row r="6" spans="1:21" s="26" customFormat="1">
       <c r="A6" s="23" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="D6" s="48"/>
       <c r="E6" s="23"/>
@@ -1848,6 +1855,7 @@
         <v>110</v>
       </c>
       <c r="T6" s="23"/>
+      <c r="U6" s="23"/>
     </row>
     <row r="7" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A7" s="23" t="s">
@@ -1857,7 +1865,7 @@
         <v>34</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="D7" s="48"/>
       <c r="E7" s="23"/>
@@ -1880,18 +1888,19 @@
       <c r="R7" s="23"/>
       <c r="S7" s="23"/>
       <c r="T7" s="23" t="s">
-        <v>184</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="U7" s="23"/>
     </row>
     <row r="8" spans="1:21" s="3" customFormat="1" ht="47.25">
       <c r="A8" s="11" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="D8" s="37"/>
       <c r="E8" s="11"/>
@@ -1912,16 +1921,17 @@
       <c r="R8" s="11"/>
       <c r="S8" s="11"/>
       <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
     </row>
     <row r="9" spans="1:21" s="3" customFormat="1" ht="78.75">
       <c r="A9" s="11" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="D9" s="37"/>
       <c r="E9" s="11"/>
@@ -1942,6 +1952,7 @@
       <c r="R9" s="11"/>
       <c r="S9" s="11"/>
       <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
     </row>
     <row r="10" spans="1:21" s="3" customFormat="1">
       <c r="A10" s="11" t="s">
@@ -1972,13 +1983,14 @@
       <c r="R10" s="11"/>
       <c r="S10" s="11"/>
       <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
     </row>
     <row r="11" spans="1:21" s="3" customFormat="1">
       <c r="A11" s="18" t="s">
         <v>62</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>90</v>
@@ -2000,6 +2012,7 @@
       <c r="R11" s="11"/>
       <c r="S11" s="11"/>
       <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
     </row>
     <row r="12" spans="1:21" s="3" customFormat="1">
       <c r="A12" s="11" t="s">
@@ -2030,6 +2043,7 @@
       <c r="R12" s="11"/>
       <c r="S12" s="11"/>
       <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
     </row>
     <row r="13" spans="1:21" s="3" customFormat="1">
       <c r="A13" s="11" t="s">
@@ -2060,23 +2074,24 @@
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
     </row>
     <row r="14" spans="1:21" s="3" customFormat="1" ht="31.5">
       <c r="A14" s="39" t="s">
         <v>10</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="D14" s="40"/>
       <c r="E14" s="39"/>
       <c r="F14" s="39"/>
       <c r="G14" s="39"/>
       <c r="H14" s="40" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="I14" s="39"/>
       <c r="J14" s="40"/>
@@ -2084,14 +2099,15 @@
       <c r="L14" s="39"/>
       <c r="M14" s="39"/>
       <c r="N14" s="39"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="41" t="s">
-        <v>108</v>
-      </c>
+      <c r="O14" s="41" t="s">
+        <v>281</v>
+      </c>
+      <c r="P14" s="41"/>
       <c r="Q14" s="11"/>
       <c r="R14" s="11"/>
       <c r="S14" s="11"/>
-      <c r="T14" s="41" t="s">
+      <c r="T14" s="41"/>
+      <c r="U14" s="41" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2116,23 +2132,24 @@
       <c r="R15" s="11"/>
       <c r="S15" s="11"/>
       <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
     </row>
     <row r="16" spans="1:21" s="3" customFormat="1">
       <c r="A16" s="42" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="B16" s="42" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="D16" s="42"/>
       <c r="E16" s="42"/>
       <c r="F16" s="42"/>
       <c r="G16" s="42"/>
       <c r="H16" s="42" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="I16" s="42"/>
       <c r="J16" s="42" t="s">
@@ -2148,23 +2165,24 @@
       <c r="R16" s="11"/>
       <c r="S16" s="11"/>
       <c r="T16" s="11"/>
-    </row>
-    <row r="17" spans="1:20" s="3" customFormat="1">
+      <c r="U16" s="11"/>
+    </row>
+    <row r="17" spans="1:21" s="3" customFormat="1">
       <c r="A17" s="42" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="D17" s="43"/>
       <c r="E17" s="42"/>
       <c r="F17" s="44"/>
       <c r="G17" s="45"/>
       <c r="H17" s="43" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="I17" s="42"/>
       <c r="J17" s="42" t="s">
@@ -2180,23 +2198,24 @@
       <c r="R17" s="11"/>
       <c r="S17" s="11"/>
       <c r="T17" s="11"/>
-    </row>
-    <row r="18" spans="1:20" s="3" customFormat="1">
+      <c r="U17" s="11"/>
+    </row>
+    <row r="18" spans="1:21" s="3" customFormat="1">
       <c r="A18" s="42" t="s">
         <v>11</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="D18" s="43"/>
       <c r="E18" s="42"/>
       <c r="F18" s="44"/>
       <c r="G18" s="45"/>
       <c r="H18" s="43" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="I18" s="42"/>
       <c r="J18" s="42" t="s">
@@ -2212,27 +2231,28 @@
       <c r="R18" s="11"/>
       <c r="S18" s="11"/>
       <c r="T18" s="11"/>
-    </row>
-    <row r="19" spans="1:20" s="3" customFormat="1" ht="31.5">
+      <c r="U18" s="11"/>
+    </row>
+    <row r="19" spans="1:21" s="3" customFormat="1" ht="31.5">
       <c r="A19" s="42" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="D19" s="43"/>
       <c r="E19" s="42"/>
       <c r="F19" s="44" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="G19" s="45" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="H19" s="43" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="I19" s="42"/>
       <c r="J19" s="42" t="s">
@@ -2248,8 +2268,9 @@
       <c r="R19" s="11"/>
       <c r="S19" s="11"/>
       <c r="T19" s="11"/>
-    </row>
-    <row r="20" spans="1:20" s="3" customFormat="1">
+      <c r="U19" s="11"/>
+    </row>
+    <row r="20" spans="1:21" s="3" customFormat="1">
       <c r="A20" s="11"/>
       <c r="B20" s="6"/>
       <c r="C20" s="37"/>
@@ -2270,8 +2291,9 @@
       <c r="R20" s="11"/>
       <c r="S20" s="11"/>
       <c r="T20" s="11"/>
-    </row>
-    <row r="21" spans="1:20" s="3" customFormat="1">
+      <c r="U20" s="11"/>
+    </row>
+    <row r="21" spans="1:21" s="3" customFormat="1">
       <c r="A21" s="46" t="s">
         <v>10</v>
       </c>
@@ -2279,7 +2301,7 @@
         <v>59</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D21" s="47"/>
       <c r="E21" s="46"/>
@@ -2287,11 +2309,11 @@
         <v>68</v>
       </c>
       <c r="G21" s="46" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="H21" s="47"/>
       <c r="I21" s="46" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="J21" s="47" t="s">
         <v>9</v>
@@ -2308,8 +2330,9 @@
       <c r="R21" s="11"/>
       <c r="S21" s="11"/>
       <c r="T21" s="11"/>
-    </row>
-    <row r="22" spans="1:20" s="3" customFormat="1">
+      <c r="U21" s="11"/>
+    </row>
+    <row r="22" spans="1:21" s="3" customFormat="1">
       <c r="A22" s="11"/>
       <c r="B22" s="6"/>
       <c r="C22" s="14"/>
@@ -2330,8 +2353,9 @@
       <c r="R22" s="11"/>
       <c r="S22" s="11"/>
       <c r="T22" s="11"/>
-    </row>
-    <row r="23" spans="1:20" s="26" customFormat="1">
+      <c r="U22" s="11"/>
+    </row>
+    <row r="23" spans="1:21" s="26" customFormat="1">
       <c r="A23" s="23" t="s">
         <v>92</v>
       </c>
@@ -2339,7 +2363,7 @@
         <v>93</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="D23" s="48"/>
       <c r="E23" s="23"/>
@@ -2360,8 +2384,9 @@
       <c r="R23" s="23"/>
       <c r="S23" s="23"/>
       <c r="T23" s="23"/>
-    </row>
-    <row r="24" spans="1:20" s="26" customFormat="1">
+      <c r="U23" s="23"/>
+    </row>
+    <row r="24" spans="1:21" s="26" customFormat="1">
       <c r="A24" s="29" t="s">
         <v>48</v>
       </c>
@@ -2369,7 +2394,7 @@
         <v>51</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="29"/>
@@ -2388,8 +2413,9 @@
       <c r="R24" s="23"/>
       <c r="S24" s="23"/>
       <c r="T24" s="23"/>
-    </row>
-    <row r="25" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U24" s="23"/>
+    </row>
+    <row r="25" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A25" s="23" t="s">
         <v>26</v>
       </c>
@@ -2397,10 +2423,10 @@
         <v>35</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="E25" s="23"/>
       <c r="F25" s="23"/>
@@ -2420,8 +2446,9 @@
       <c r="R25" s="23"/>
       <c r="S25" s="23"/>
       <c r="T25" s="23"/>
-    </row>
-    <row r="26" spans="1:20" s="26" customFormat="1">
+      <c r="U25" s="23"/>
+    </row>
+    <row r="26" spans="1:21" s="26" customFormat="1">
       <c r="A26" s="23"/>
       <c r="B26" s="28"/>
       <c r="C26" s="48"/>
@@ -2442,8 +2469,9 @@
       <c r="R26" s="23"/>
       <c r="S26" s="23"/>
       <c r="T26" s="23"/>
-    </row>
-    <row r="27" spans="1:20" s="26" customFormat="1">
+      <c r="U26" s="23"/>
+    </row>
+    <row r="27" spans="1:21" s="26" customFormat="1">
       <c r="A27" s="10" t="s">
         <v>48</v>
       </c>
@@ -2451,7 +2479,7 @@
         <v>53</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="33"/>
@@ -2470,16 +2498,17 @@
       <c r="R27" s="23"/>
       <c r="S27" s="23"/>
       <c r="T27" s="23"/>
-    </row>
-    <row r="28" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U27" s="23"/>
+    </row>
+    <row r="28" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A28" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>49</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="D28" s="37"/>
       <c r="E28" s="11"/>
@@ -2500,16 +2529,17 @@
       <c r="R28" s="23"/>
       <c r="S28" s="23"/>
       <c r="T28" s="23"/>
-    </row>
-    <row r="29" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U28" s="23"/>
+    </row>
+    <row r="29" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A29" s="6" t="s">
         <v>94</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="D29" s="37"/>
       <c r="E29" s="11"/>
@@ -2530,8 +2560,9 @@
       <c r="R29" s="23"/>
       <c r="S29" s="23"/>
       <c r="T29" s="23"/>
-    </row>
-    <row r="30" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U29" s="23"/>
+    </row>
+    <row r="30" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A30" s="6" t="s">
         <v>12</v>
       </c>
@@ -2539,14 +2570,14 @@
         <v>50</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="D30" s="37"/>
       <c r="E30" s="11"/>
       <c r="F30" s="6"/>
       <c r="G30" s="50"/>
       <c r="H30" s="11" t="s">
-        <v>121</v>
+        <v>283</v>
       </c>
       <c r="I30" s="11"/>
       <c r="J30" s="6" t="s">
@@ -2562,8 +2593,9 @@
       <c r="R30" s="23"/>
       <c r="S30" s="23"/>
       <c r="T30" s="23"/>
-    </row>
-    <row r="31" spans="1:20" s="26" customFormat="1">
+      <c r="U30" s="23"/>
+    </row>
+    <row r="31" spans="1:21" s="26" customFormat="1">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="37"/>
@@ -2584,8 +2616,9 @@
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
-    </row>
-    <row r="32" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U31" s="23"/>
+    </row>
+    <row r="32" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A32" s="6" t="s">
         <v>12</v>
       </c>
@@ -2593,16 +2626,16 @@
         <v>54</v>
       </c>
       <c r="C32" s="37" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="6"/>
       <c r="G32" s="50"/>
       <c r="H32" s="11" t="s">
-        <v>121</v>
+        <v>283</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>55</v>
@@ -2622,8 +2655,9 @@
       <c r="R32" s="23"/>
       <c r="S32" s="23"/>
       <c r="T32" s="23"/>
-    </row>
-    <row r="33" spans="1:20" s="26" customFormat="1">
+      <c r="U32" s="23"/>
+    </row>
+    <row r="33" spans="1:21" s="26" customFormat="1">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="37"/>
@@ -2644,8 +2678,9 @@
       <c r="R33" s="23"/>
       <c r="S33" s="23"/>
       <c r="T33" s="23"/>
-    </row>
-    <row r="34" spans="1:20" s="26" customFormat="1">
+      <c r="U33" s="23"/>
+    </row>
+    <row r="34" spans="1:21" s="26" customFormat="1">
       <c r="A34" s="29" t="s">
         <v>48</v>
       </c>
@@ -2653,14 +2688,14 @@
         <v>52</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="D34" s="31"/>
       <c r="E34" s="29"/>
       <c r="F34" s="29"/>
       <c r="G34" s="31"/>
       <c r="H34" s="11" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="I34" s="29"/>
       <c r="J34" s="29"/>
@@ -2674,8 +2709,9 @@
       <c r="R34" s="23"/>
       <c r="S34" s="23"/>
       <c r="T34" s="23"/>
-    </row>
-    <row r="35" spans="1:20" s="26" customFormat="1">
+      <c r="U34" s="23"/>
+    </row>
+    <row r="35" spans="1:21" s="26" customFormat="1">
       <c r="A35" s="29" t="s">
         <v>94</v>
       </c>
@@ -2683,14 +2719,14 @@
         <v>95</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="D35" s="31"/>
       <c r="E35" s="29"/>
       <c r="F35" s="29"/>
       <c r="G35" s="31"/>
       <c r="H35" s="11" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="I35" s="29"/>
       <c r="J35" s="29"/>
@@ -2704,8 +2740,9 @@
       <c r="R35" s="23"/>
       <c r="S35" s="23"/>
       <c r="T35" s="23"/>
-    </row>
-    <row r="36" spans="1:20" s="26" customFormat="1">
+      <c r="U35" s="23"/>
+    </row>
+    <row r="36" spans="1:21" s="26" customFormat="1">
       <c r="A36" s="29"/>
       <c r="B36" s="30"/>
       <c r="C36" s="31"/>
@@ -2726,8 +2763,9 @@
       <c r="R36" s="23"/>
       <c r="S36" s="23"/>
       <c r="T36" s="23"/>
-    </row>
-    <row r="37" spans="1:20" s="26" customFormat="1">
+      <c r="U36" s="23"/>
+    </row>
+    <row r="37" spans="1:21" s="26" customFormat="1">
       <c r="A37" s="6" t="s">
         <v>12</v>
       </c>
@@ -2735,14 +2773,14 @@
         <v>36</v>
       </c>
       <c r="C37" s="37" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="D37" s="37"/>
       <c r="E37" s="11"/>
       <c r="F37" s="6"/>
       <c r="G37" s="50"/>
       <c r="H37" s="11" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="I37" s="11"/>
       <c r="J37" s="6" t="s">
@@ -2758,8 +2796,9 @@
       <c r="R37" s="23"/>
       <c r="S37" s="23"/>
       <c r="T37" s="23"/>
-    </row>
-    <row r="38" spans="1:20" s="26" customFormat="1">
+      <c r="U37" s="23"/>
+    </row>
+    <row r="38" spans="1:21" s="26" customFormat="1">
       <c r="A38" s="6" t="s">
         <v>12</v>
       </c>
@@ -2767,14 +2806,14 @@
         <v>37</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="D38" s="37"/>
       <c r="E38" s="11"/>
       <c r="F38" s="6"/>
       <c r="G38" s="50"/>
       <c r="H38" s="11" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="I38" s="11"/>
       <c r="J38" s="6" t="s">
@@ -2790,8 +2829,9 @@
       <c r="R38" s="23"/>
       <c r="S38" s="23"/>
       <c r="T38" s="23"/>
-    </row>
-    <row r="39" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U38" s="23"/>
+    </row>
+    <row r="39" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A39" s="6" t="s">
         <v>12</v>
       </c>
@@ -2799,16 +2839,16 @@
         <v>74</v>
       </c>
       <c r="C39" s="48" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="D39" s="48" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E39" s="23"/>
       <c r="F39" s="23"/>
       <c r="G39" s="48"/>
       <c r="H39" s="23" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="I39" s="23" t="s">
         <v>56</v>
@@ -2828,8 +2868,9 @@
       <c r="R39" s="23"/>
       <c r="S39" s="23"/>
       <c r="T39" s="23"/>
-    </row>
-    <row r="40" spans="1:20" s="3" customFormat="1" ht="31.5">
+      <c r="U39" s="23"/>
+    </row>
+    <row r="40" spans="1:21" s="3" customFormat="1" ht="31.5">
       <c r="A40" s="6" t="s">
         <v>60</v>
       </c>
@@ -2842,7 +2883,7 @@
       <c r="F40" s="6"/>
       <c r="G40" s="50"/>
       <c r="H40" s="23" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>71</v>
@@ -2858,8 +2899,9 @@
       <c r="R40" s="11"/>
       <c r="S40" s="11"/>
       <c r="T40" s="11"/>
-    </row>
-    <row r="41" spans="1:20" s="3" customFormat="1" ht="31.5">
+      <c r="U40" s="11"/>
+    </row>
+    <row r="41" spans="1:21" s="3" customFormat="1" ht="31.5">
       <c r="A41" s="6" t="s">
         <v>60</v>
       </c>
@@ -2872,7 +2914,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="50"/>
       <c r="H41" s="23" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="I41" s="11" t="s">
         <v>73</v>
@@ -2888,8 +2930,9 @@
       <c r="R41" s="11"/>
       <c r="S41" s="11"/>
       <c r="T41" s="11"/>
-    </row>
-    <row r="42" spans="1:20" s="26" customFormat="1">
+      <c r="U41" s="11"/>
+    </row>
+    <row r="42" spans="1:21" s="26" customFormat="1">
       <c r="A42" s="6"/>
       <c r="B42" s="28"/>
       <c r="C42" s="48"/>
@@ -2910,8 +2953,9 @@
       <c r="R42" s="23"/>
       <c r="S42" s="23"/>
       <c r="T42" s="23"/>
-    </row>
-    <row r="43" spans="1:20" s="26" customFormat="1">
+      <c r="U42" s="23"/>
+    </row>
+    <row r="43" spans="1:21" s="26" customFormat="1">
       <c r="A43" s="6" t="s">
         <v>12</v>
       </c>
@@ -2919,14 +2963,14 @@
         <v>38</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="D43" s="37"/>
       <c r="E43" s="11"/>
       <c r="F43" s="6"/>
       <c r="G43" s="50"/>
       <c r="H43" s="11" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="I43" s="11"/>
       <c r="J43" s="6" t="s">
@@ -2942,8 +2986,9 @@
       <c r="R43" s="23"/>
       <c r="S43" s="23"/>
       <c r="T43" s="23"/>
-    </row>
-    <row r="44" spans="1:20" s="26" customFormat="1">
+      <c r="U43" s="23"/>
+    </row>
+    <row r="44" spans="1:21" s="26" customFormat="1">
       <c r="A44" s="6" t="s">
         <v>12</v>
       </c>
@@ -2951,14 +2996,14 @@
         <v>39</v>
       </c>
       <c r="C44" s="37" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="D44" s="37"/>
       <c r="E44" s="11"/>
       <c r="F44" s="6"/>
       <c r="G44" s="50"/>
       <c r="H44" s="11" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="I44" s="11"/>
       <c r="J44" s="6" t="s">
@@ -2974,8 +3019,9 @@
       <c r="R44" s="23"/>
       <c r="S44" s="23"/>
       <c r="T44" s="23"/>
-    </row>
-    <row r="45" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U44" s="23"/>
+    </row>
+    <row r="45" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A45" s="6" t="s">
         <v>12</v>
       </c>
@@ -2983,16 +3029,16 @@
         <v>79</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="D45" s="37" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E45" s="11"/>
       <c r="F45" s="6"/>
       <c r="G45" s="50"/>
       <c r="H45" s="11" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="I45" s="23" t="s">
         <v>57</v>
@@ -3012,8 +3058,9 @@
       <c r="R45" s="23"/>
       <c r="S45" s="23"/>
       <c r="T45" s="23"/>
-    </row>
-    <row r="46" spans="1:20" s="3" customFormat="1" ht="31.5">
+      <c r="U45" s="23"/>
+    </row>
+    <row r="46" spans="1:21" s="3" customFormat="1" ht="31.5">
       <c r="A46" s="6" t="s">
         <v>60</v>
       </c>
@@ -3026,7 +3073,7 @@
       <c r="F46" s="6"/>
       <c r="G46" s="50"/>
       <c r="H46" s="23" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="I46" s="11" t="s">
         <v>76</v>
@@ -3042,8 +3089,9 @@
       <c r="R46" s="11"/>
       <c r="S46" s="11"/>
       <c r="T46" s="11"/>
-    </row>
-    <row r="47" spans="1:20" s="3" customFormat="1" ht="31.5">
+      <c r="U46" s="11"/>
+    </row>
+    <row r="47" spans="1:21" s="3" customFormat="1" ht="31.5">
       <c r="A47" s="6" t="s">
         <v>60</v>
       </c>
@@ -3056,7 +3104,7 @@
       <c r="F47" s="6"/>
       <c r="G47" s="50"/>
       <c r="H47" s="23" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="I47" s="11" t="s">
         <v>78</v>
@@ -3072,8 +3120,9 @@
       <c r="R47" s="11"/>
       <c r="S47" s="11"/>
       <c r="T47" s="11"/>
-    </row>
-    <row r="48" spans="1:20" s="26" customFormat="1">
+      <c r="U47" s="11"/>
+    </row>
+    <row r="48" spans="1:21" s="26" customFormat="1">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="37"/>
@@ -3094,8 +3143,9 @@
       <c r="R48" s="23"/>
       <c r="S48" s="23"/>
       <c r="T48" s="23"/>
-    </row>
-    <row r="49" spans="1:20" s="26" customFormat="1">
+      <c r="U48" s="23"/>
+    </row>
+    <row r="49" spans="1:21" s="26" customFormat="1">
       <c r="A49" s="6" t="s">
         <v>12</v>
       </c>
@@ -3103,14 +3153,14 @@
         <v>40</v>
       </c>
       <c r="C49" s="37" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="D49" s="37"/>
       <c r="E49" s="11"/>
       <c r="F49" s="6"/>
       <c r="G49" s="50"/>
       <c r="H49" s="11" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="I49" s="23"/>
       <c r="J49" s="6" t="s">
@@ -3126,8 +3176,9 @@
       <c r="R49" s="23"/>
       <c r="S49" s="23"/>
       <c r="T49" s="23"/>
-    </row>
-    <row r="50" spans="1:20" s="26" customFormat="1">
+      <c r="U49" s="23"/>
+    </row>
+    <row r="50" spans="1:21" s="26" customFormat="1">
       <c r="A50" s="6" t="s">
         <v>12</v>
       </c>
@@ -3135,14 +3186,14 @@
         <v>41</v>
       </c>
       <c r="C50" s="37" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="D50" s="37"/>
       <c r="E50" s="11"/>
       <c r="F50" s="6"/>
       <c r="G50" s="50"/>
       <c r="H50" s="11" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="I50" s="11"/>
       <c r="J50" s="6" t="s">
@@ -3158,8 +3209,9 @@
       <c r="R50" s="23"/>
       <c r="S50" s="23"/>
       <c r="T50" s="23"/>
-    </row>
-    <row r="51" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U50" s="23"/>
+    </row>
+    <row r="51" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A51" s="6" t="s">
         <v>12</v>
       </c>
@@ -3167,16 +3219,16 @@
         <v>84</v>
       </c>
       <c r="C51" s="37" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="D51" s="37" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E51" s="11"/>
       <c r="F51" s="6"/>
       <c r="G51" s="50"/>
       <c r="H51" s="11" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="I51" s="23" t="s">
         <v>96</v>
@@ -3196,8 +3248,9 @@
       <c r="R51" s="23"/>
       <c r="S51" s="23"/>
       <c r="T51" s="23"/>
-    </row>
-    <row r="52" spans="1:20" s="3" customFormat="1" ht="31.5">
+      <c r="U51" s="23"/>
+    </row>
+    <row r="52" spans="1:21" s="3" customFormat="1" ht="31.5">
       <c r="A52" s="6" t="s">
         <v>60</v>
       </c>
@@ -3210,7 +3263,7 @@
       <c r="F52" s="6"/>
       <c r="G52" s="50"/>
       <c r="H52" s="23" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="I52" s="11" t="s">
         <v>81</v>
@@ -3226,8 +3279,9 @@
       <c r="R52" s="11"/>
       <c r="S52" s="11"/>
       <c r="T52" s="11"/>
-    </row>
-    <row r="53" spans="1:20" s="3" customFormat="1" ht="31.5">
+      <c r="U52" s="11"/>
+    </row>
+    <row r="53" spans="1:21" s="3" customFormat="1" ht="31.5">
       <c r="A53" s="6" t="s">
         <v>60</v>
       </c>
@@ -3240,7 +3294,7 @@
       <c r="F53" s="6"/>
       <c r="G53" s="50"/>
       <c r="H53" s="23" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="I53" s="11" t="s">
         <v>83</v>
@@ -3256,8 +3310,9 @@
       <c r="R53" s="11"/>
       <c r="S53" s="11"/>
       <c r="T53" s="11"/>
-    </row>
-    <row r="54" spans="1:20" s="26" customFormat="1">
+      <c r="U53" s="11"/>
+    </row>
+    <row r="54" spans="1:21" s="26" customFormat="1">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="37"/>
@@ -3278,8 +3333,9 @@
       <c r="R54" s="23"/>
       <c r="S54" s="23"/>
       <c r="T54" s="23"/>
-    </row>
-    <row r="55" spans="1:20" s="26" customFormat="1">
+      <c r="U54" s="23"/>
+    </row>
+    <row r="55" spans="1:21" s="26" customFormat="1">
       <c r="A55" s="6" t="s">
         <v>12</v>
       </c>
@@ -3287,14 +3343,14 @@
         <v>42</v>
       </c>
       <c r="C55" s="37" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="D55" s="37"/>
       <c r="E55" s="11"/>
       <c r="F55" s="6"/>
       <c r="G55" s="50"/>
       <c r="H55" s="11" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="I55" s="11"/>
       <c r="J55" s="6" t="s">
@@ -3310,8 +3366,9 @@
       <c r="R55" s="23"/>
       <c r="S55" s="23"/>
       <c r="T55" s="23"/>
-    </row>
-    <row r="56" spans="1:20" s="26" customFormat="1">
+      <c r="U55" s="23"/>
+    </row>
+    <row r="56" spans="1:21" s="26" customFormat="1">
       <c r="A56" s="6" t="s">
         <v>12</v>
       </c>
@@ -3319,14 +3376,14 @@
         <v>43</v>
       </c>
       <c r="C56" s="37" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="D56" s="37"/>
       <c r="E56" s="11"/>
       <c r="F56" s="6"/>
       <c r="G56" s="50"/>
       <c r="H56" s="11" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="I56" s="11"/>
       <c r="J56" s="6" t="s">
@@ -3342,8 +3399,9 @@
       <c r="R56" s="23"/>
       <c r="S56" s="23"/>
       <c r="T56" s="23"/>
-    </row>
-    <row r="57" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U56" s="23"/>
+    </row>
+    <row r="57" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A57" s="6" t="s">
         <v>12</v>
       </c>
@@ -3351,16 +3409,16 @@
         <v>89</v>
       </c>
       <c r="C57" s="37" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="D57" s="37" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="6"/>
       <c r="G57" s="50"/>
       <c r="H57" s="11" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="I57" s="23" t="s">
         <v>58</v>
@@ -3380,8 +3438,9 @@
       <c r="R57" s="23"/>
       <c r="S57" s="23"/>
       <c r="T57" s="23"/>
-    </row>
-    <row r="58" spans="1:20" s="3" customFormat="1" ht="31.5">
+      <c r="U57" s="23"/>
+    </row>
+    <row r="58" spans="1:21" s="3" customFormat="1" ht="31.5">
       <c r="A58" s="6" t="s">
         <v>60</v>
       </c>
@@ -3394,7 +3453,7 @@
       <c r="F58" s="6"/>
       <c r="G58" s="50"/>
       <c r="H58" s="23" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="I58" s="11" t="s">
         <v>86</v>
@@ -3410,8 +3469,9 @@
       <c r="R58" s="11"/>
       <c r="S58" s="11"/>
       <c r="T58" s="11"/>
-    </row>
-    <row r="59" spans="1:20" s="3" customFormat="1" ht="31.5">
+      <c r="U58" s="11"/>
+    </row>
+    <row r="59" spans="1:21" s="3" customFormat="1" ht="31.5">
       <c r="A59" s="6" t="s">
         <v>60</v>
       </c>
@@ -3424,7 +3484,7 @@
       <c r="F59" s="6"/>
       <c r="G59" s="50"/>
       <c r="H59" s="23" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="I59" s="11" t="s">
         <v>88</v>
@@ -3440,8 +3500,9 @@
       <c r="R59" s="11"/>
       <c r="S59" s="11"/>
       <c r="T59" s="11"/>
-    </row>
-    <row r="60" spans="1:20" s="3" customFormat="1">
+      <c r="U59" s="11"/>
+    </row>
+    <row r="60" spans="1:21" s="3" customFormat="1">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="37"/>
@@ -3462,23 +3523,24 @@
       <c r="R60" s="11"/>
       <c r="S60" s="11"/>
       <c r="T60" s="11"/>
-    </row>
-    <row r="61" spans="1:20" s="3" customFormat="1">
+      <c r="U60" s="11"/>
+    </row>
+    <row r="61" spans="1:21" s="3" customFormat="1">
       <c r="A61" s="29" t="s">
         <v>94</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C61" s="37" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="D61" s="37"/>
       <c r="E61" s="11"/>
       <c r="F61" s="6"/>
       <c r="G61" s="50"/>
       <c r="H61" s="23" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="I61" s="11"/>
       <c r="J61" s="6" t="s">
@@ -3494,23 +3556,24 @@
       <c r="R61" s="11"/>
       <c r="S61" s="11"/>
       <c r="T61" s="11"/>
-    </row>
-    <row r="62" spans="1:20" s="3" customFormat="1" ht="31.5">
+      <c r="U61" s="11"/>
+    </row>
+    <row r="62" spans="1:21" s="3" customFormat="1" ht="31.5">
       <c r="A62" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C62" s="37" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="D62" s="37"/>
       <c r="E62" s="11"/>
       <c r="F62" s="6"/>
       <c r="G62" s="50"/>
       <c r="H62" s="23" t="s">
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="I62" s="11"/>
       <c r="J62" s="6"/>
@@ -3524,8 +3587,9 @@
       <c r="R62" s="11"/>
       <c r="S62" s="11"/>
       <c r="T62" s="11"/>
-    </row>
-    <row r="63" spans="1:20" s="3" customFormat="1">
+      <c r="U62" s="11"/>
+    </row>
+    <row r="63" spans="1:21" s="3" customFormat="1">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="37"/>
@@ -3546,23 +3610,24 @@
       <c r="R63" s="11"/>
       <c r="S63" s="11"/>
       <c r="T63" s="11"/>
-    </row>
-    <row r="64" spans="1:20" s="26" customFormat="1">
+      <c r="U63" s="11"/>
+    </row>
+    <row r="64" spans="1:21" s="26" customFormat="1">
       <c r="A64" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C64" s="37" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="D64" s="37"/>
       <c r="E64" s="11"/>
       <c r="F64" s="6"/>
       <c r="G64" s="50"/>
       <c r="H64" s="11" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I64" s="11"/>
       <c r="J64" s="6" t="s">
@@ -3578,23 +3643,24 @@
       <c r="R64" s="23"/>
       <c r="S64" s="23"/>
       <c r="T64" s="23"/>
-    </row>
-    <row r="65" spans="1:20" s="26" customFormat="1">
+      <c r="U64" s="23"/>
+    </row>
+    <row r="65" spans="1:21" s="26" customFormat="1">
       <c r="A65" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C65" s="37" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="D65" s="37"/>
       <c r="E65" s="11"/>
       <c r="F65" s="6"/>
       <c r="G65" s="50"/>
       <c r="H65" s="11" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I65" s="11"/>
       <c r="J65" s="6" t="s">
@@ -3610,28 +3676,29 @@
       <c r="R65" s="23"/>
       <c r="S65" s="23"/>
       <c r="T65" s="23"/>
-    </row>
-    <row r="66" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U65" s="23"/>
+    </row>
+    <row r="66" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A66" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C66" s="37" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="D66" s="37" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E66" s="11"/>
       <c r="F66" s="6"/>
       <c r="G66" s="50"/>
       <c r="H66" s="11" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I66" s="23" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="J66" s="6" t="s">
         <v>9</v>
@@ -3648,8 +3715,9 @@
       <c r="R66" s="23"/>
       <c r="S66" s="23"/>
       <c r="T66" s="23"/>
-    </row>
-    <row r="67" spans="1:20" s="3" customFormat="1">
+      <c r="U66" s="23"/>
+    </row>
+    <row r="67" spans="1:21" s="3" customFormat="1">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="37"/>
@@ -3670,23 +3738,24 @@
       <c r="R67" s="11"/>
       <c r="S67" s="11"/>
       <c r="T67" s="11"/>
-    </row>
-    <row r="68" spans="1:20" s="26" customFormat="1">
+      <c r="U67" s="11"/>
+    </row>
+    <row r="68" spans="1:21" s="26" customFormat="1">
       <c r="A68" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C68" s="37" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="D68" s="37"/>
       <c r="E68" s="11"/>
       <c r="F68" s="6"/>
       <c r="G68" s="50"/>
       <c r="H68" s="11" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I68" s="11"/>
       <c r="J68" s="6" t="s">
@@ -3702,23 +3771,24 @@
       <c r="R68" s="23"/>
       <c r="S68" s="23"/>
       <c r="T68" s="23"/>
-    </row>
-    <row r="69" spans="1:20" s="26" customFormat="1">
+      <c r="U68" s="23"/>
+    </row>
+    <row r="69" spans="1:21" s="26" customFormat="1">
       <c r="A69" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C69" s="37" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="D69" s="37"/>
       <c r="E69" s="11"/>
       <c r="F69" s="6"/>
       <c r="G69" s="50"/>
       <c r="H69" s="11" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I69" s="11"/>
       <c r="J69" s="6" t="s">
@@ -3734,28 +3804,29 @@
       <c r="R69" s="23"/>
       <c r="S69" s="23"/>
       <c r="T69" s="23"/>
-    </row>
-    <row r="70" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U69" s="23"/>
+    </row>
+    <row r="70" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A70" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C70" s="37" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E70" s="11"/>
       <c r="F70" s="6"/>
       <c r="G70" s="50"/>
       <c r="H70" s="11" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I70" s="23" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="J70" s="6" t="s">
         <v>9</v>
@@ -3772,8 +3843,9 @@
       <c r="R70" s="23"/>
       <c r="S70" s="23"/>
       <c r="T70" s="23"/>
-    </row>
-    <row r="71" spans="1:20" s="3" customFormat="1">
+      <c r="U70" s="23"/>
+    </row>
+    <row r="71" spans="1:21" s="3" customFormat="1">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="37"/>
@@ -3794,23 +3866,24 @@
       <c r="R71" s="11"/>
       <c r="S71" s="11"/>
       <c r="T71" s="11"/>
-    </row>
-    <row r="72" spans="1:20" s="26" customFormat="1">
+      <c r="U71" s="11"/>
+    </row>
+    <row r="72" spans="1:21" s="26" customFormat="1">
       <c r="A72" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C72" s="37" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="D72" s="37"/>
       <c r="E72" s="11"/>
       <c r="F72" s="6"/>
       <c r="G72" s="50"/>
       <c r="H72" s="11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I72" s="11"/>
       <c r="J72" s="6" t="s">
@@ -3826,23 +3899,24 @@
       <c r="R72" s="23"/>
       <c r="S72" s="23"/>
       <c r="T72" s="23"/>
-    </row>
-    <row r="73" spans="1:20" s="26" customFormat="1">
+      <c r="U72" s="23"/>
+    </row>
+    <row r="73" spans="1:21" s="26" customFormat="1">
       <c r="A73" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C73" s="37" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="D73" s="37"/>
       <c r="E73" s="11"/>
       <c r="F73" s="6"/>
       <c r="G73" s="50"/>
       <c r="H73" s="11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I73" s="11"/>
       <c r="J73" s="6" t="s">
@@ -3858,28 +3932,29 @@
       <c r="R73" s="23"/>
       <c r="S73" s="23"/>
       <c r="T73" s="23"/>
-    </row>
-    <row r="74" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U73" s="23"/>
+    </row>
+    <row r="74" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A74" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C74" s="37" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="D74" s="37" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="6"/>
       <c r="G74" s="50"/>
       <c r="H74" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="I74" s="23" t="s">
         <v>149</v>
-      </c>
-      <c r="I74" s="23" t="s">
-        <v>153</v>
       </c>
       <c r="J74" s="6" t="s">
         <v>9</v>
@@ -3896,8 +3971,9 @@
       <c r="R74" s="23"/>
       <c r="S74" s="23"/>
       <c r="T74" s="23"/>
-    </row>
-    <row r="75" spans="1:20" s="3" customFormat="1">
+      <c r="U74" s="23"/>
+    </row>
+    <row r="75" spans="1:21" s="3" customFormat="1">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="37"/>
@@ -3918,23 +3994,24 @@
       <c r="R75" s="11"/>
       <c r="S75" s="11"/>
       <c r="T75" s="11"/>
-    </row>
-    <row r="76" spans="1:20" s="26" customFormat="1">
+      <c r="U75" s="11"/>
+    </row>
+    <row r="76" spans="1:21" s="26" customFormat="1">
       <c r="A76" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C76" s="37" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="D76" s="37"/>
       <c r="E76" s="11"/>
       <c r="F76" s="6"/>
       <c r="G76" s="50"/>
       <c r="H76" s="11" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I76" s="11"/>
       <c r="J76" s="6" t="s">
@@ -3950,23 +4027,24 @@
       <c r="R76" s="23"/>
       <c r="S76" s="23"/>
       <c r="T76" s="23"/>
-    </row>
-    <row r="77" spans="1:20" s="26" customFormat="1">
+      <c r="U76" s="23"/>
+    </row>
+    <row r="77" spans="1:21" s="26" customFormat="1">
       <c r="A77" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C77" s="37" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="D77" s="37"/>
       <c r="E77" s="11"/>
       <c r="F77" s="6"/>
       <c r="G77" s="50"/>
       <c r="H77" s="11" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I77" s="11"/>
       <c r="J77" s="6" t="s">
@@ -3982,28 +4060,29 @@
       <c r="R77" s="23"/>
       <c r="S77" s="23"/>
       <c r="T77" s="23"/>
-    </row>
-    <row r="78" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U77" s="23"/>
+    </row>
+    <row r="78" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A78" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C78" s="37" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="D78" s="37" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E78" s="11"/>
       <c r="F78" s="6"/>
       <c r="G78" s="50"/>
       <c r="H78" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="I78" s="23" t="s">
         <v>154</v>
-      </c>
-      <c r="I78" s="23" t="s">
-        <v>158</v>
       </c>
       <c r="J78" s="6" t="s">
         <v>9</v>
@@ -4020,8 +4099,9 @@
       <c r="R78" s="23"/>
       <c r="S78" s="23"/>
       <c r="T78" s="23"/>
-    </row>
-    <row r="79" spans="1:20" s="3" customFormat="1">
+      <c r="U78" s="23"/>
+    </row>
+    <row r="79" spans="1:21" s="3" customFormat="1">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="37"/>
@@ -4042,23 +4122,24 @@
       <c r="R79" s="11"/>
       <c r="S79" s="11"/>
       <c r="T79" s="11"/>
-    </row>
-    <row r="80" spans="1:20" s="26" customFormat="1">
+      <c r="U79" s="11"/>
+    </row>
+    <row r="80" spans="1:21" s="26" customFormat="1">
       <c r="A80" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>160</v>
+        <v>293</v>
       </c>
       <c r="C80" s="37" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="D80" s="37"/>
       <c r="E80" s="11"/>
       <c r="F80" s="6"/>
       <c r="G80" s="50"/>
       <c r="H80" s="11" t="s">
-        <v>159</v>
+        <v>294</v>
       </c>
       <c r="I80" s="11"/>
       <c r="J80" s="6" t="s">
@@ -4074,23 +4155,24 @@
       <c r="R80" s="23"/>
       <c r="S80" s="23"/>
       <c r="T80" s="23"/>
-    </row>
-    <row r="81" spans="1:20" s="26" customFormat="1">
+      <c r="U80" s="23"/>
+    </row>
+    <row r="81" spans="1:21" s="26" customFormat="1">
       <c r="A81" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>161</v>
+        <v>295</v>
       </c>
       <c r="C81" s="37" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="D81" s="37"/>
       <c r="E81" s="11"/>
       <c r="F81" s="6"/>
       <c r="G81" s="50"/>
       <c r="H81" s="11" t="s">
-        <v>159</v>
+        <v>294</v>
       </c>
       <c r="I81" s="11"/>
       <c r="J81" s="6" t="s">
@@ -4106,28 +4188,29 @@
       <c r="R81" s="23"/>
       <c r="S81" s="23"/>
       <c r="T81" s="23"/>
-    </row>
-    <row r="82" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U81" s="23"/>
+    </row>
+    <row r="82" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A82" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>162</v>
+        <v>296</v>
       </c>
       <c r="C82" s="37" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="D82" s="37" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="6"/>
       <c r="G82" s="50"/>
       <c r="H82" s="11" t="s">
-        <v>159</v>
+        <v>294</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>163</v>
+        <v>297</v>
       </c>
       <c r="J82" s="6" t="s">
         <v>9</v>
@@ -4144,8 +4227,9 @@
       <c r="R82" s="23"/>
       <c r="S82" s="23"/>
       <c r="T82" s="23"/>
-    </row>
-    <row r="83" spans="1:20" s="3" customFormat="1">
+      <c r="U82" s="23"/>
+    </row>
+    <row r="83" spans="1:21" s="3" customFormat="1">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="37"/>
@@ -4166,23 +4250,24 @@
       <c r="R83" s="11"/>
       <c r="S83" s="11"/>
       <c r="T83" s="11"/>
-    </row>
-    <row r="84" spans="1:20" s="26" customFormat="1">
+      <c r="U83" s="11"/>
+    </row>
+    <row r="84" spans="1:21" s="26" customFormat="1">
       <c r="A84" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C84" s="37" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="D84" s="37"/>
       <c r="E84" s="11"/>
       <c r="F84" s="6"/>
       <c r="G84" s="50"/>
       <c r="H84" s="11" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="I84" s="11"/>
       <c r="J84" s="6" t="s">
@@ -4198,23 +4283,24 @@
       <c r="R84" s="23"/>
       <c r="S84" s="23"/>
       <c r="T84" s="23"/>
-    </row>
-    <row r="85" spans="1:20" s="26" customFormat="1">
+      <c r="U84" s="23"/>
+    </row>
+    <row r="85" spans="1:21" s="26" customFormat="1">
       <c r="A85" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C85" s="37" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="D85" s="37"/>
       <c r="E85" s="11"/>
       <c r="F85" s="6"/>
       <c r="G85" s="50"/>
       <c r="H85" s="11" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="I85" s="11"/>
       <c r="J85" s="6" t="s">
@@ -4230,28 +4316,29 @@
       <c r="R85" s="23"/>
       <c r="S85" s="23"/>
       <c r="T85" s="23"/>
-    </row>
-    <row r="86" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U85" s="23"/>
+    </row>
+    <row r="86" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A86" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C86" s="37" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="D86" s="37" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E86" s="11"/>
       <c r="F86" s="6"/>
       <c r="G86" s="50"/>
       <c r="H86" s="11" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="I86" s="23" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="J86" s="6" t="s">
         <v>9</v>
@@ -4268,8 +4355,9 @@
       <c r="R86" s="23"/>
       <c r="S86" s="23"/>
       <c r="T86" s="23"/>
-    </row>
-    <row r="87" spans="1:20" s="3" customFormat="1">
+      <c r="U86" s="23"/>
+    </row>
+    <row r="87" spans="1:21" s="3" customFormat="1">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="37"/>
@@ -4290,23 +4378,24 @@
       <c r="R87" s="11"/>
       <c r="S87" s="11"/>
       <c r="T87" s="11"/>
-    </row>
-    <row r="88" spans="1:20" s="26" customFormat="1">
+      <c r="U87" s="11"/>
+    </row>
+    <row r="88" spans="1:21" s="26" customFormat="1">
       <c r="A88" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C88" s="37" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="D88" s="37"/>
       <c r="E88" s="11"/>
       <c r="F88" s="6"/>
       <c r="G88" s="50"/>
       <c r="H88" s="11" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="I88" s="11"/>
       <c r="J88" s="6" t="s">
@@ -4322,23 +4411,24 @@
       <c r="R88" s="23"/>
       <c r="S88" s="23"/>
       <c r="T88" s="23"/>
-    </row>
-    <row r="89" spans="1:20" s="26" customFormat="1">
+      <c r="U88" s="23"/>
+    </row>
+    <row r="89" spans="1:21" s="26" customFormat="1">
       <c r="A89" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C89" s="37" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D89" s="37"/>
       <c r="E89" s="11"/>
       <c r="F89" s="6"/>
       <c r="G89" s="50"/>
       <c r="H89" s="11" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="I89" s="11"/>
       <c r="J89" s="6" t="s">
@@ -4354,28 +4444,29 @@
       <c r="R89" s="23"/>
       <c r="S89" s="23"/>
       <c r="T89" s="23"/>
-    </row>
-    <row r="90" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U89" s="23"/>
+    </row>
+    <row r="90" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A90" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C90" s="37" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="D90" s="37" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="6"/>
       <c r="G90" s="50"/>
       <c r="H90" s="11" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="I90" s="23" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="J90" s="6" t="s">
         <v>9</v>
@@ -4392,8 +4483,9 @@
       <c r="R90" s="23"/>
       <c r="S90" s="23"/>
       <c r="T90" s="23"/>
-    </row>
-    <row r="91" spans="1:20" s="3" customFormat="1">
+      <c r="U90" s="23"/>
+    </row>
+    <row r="91" spans="1:21" s="3" customFormat="1">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="37"/>
@@ -4414,23 +4506,24 @@
       <c r="R91" s="11"/>
       <c r="S91" s="11"/>
       <c r="T91" s="11"/>
-    </row>
-    <row r="92" spans="1:20" s="26" customFormat="1">
+      <c r="U91" s="11"/>
+    </row>
+    <row r="92" spans="1:21" s="26" customFormat="1">
       <c r="A92" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>176</v>
+        <v>286</v>
       </c>
       <c r="C92" s="37" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="D92" s="37"/>
       <c r="E92" s="11"/>
       <c r="F92" s="6"/>
       <c r="G92" s="50"/>
       <c r="H92" s="11" t="s">
-        <v>175</v>
+        <v>287</v>
       </c>
       <c r="I92" s="11"/>
       <c r="J92" s="6" t="s">
@@ -4446,23 +4539,24 @@
       <c r="R92" s="23"/>
       <c r="S92" s="23"/>
       <c r="T92" s="23"/>
-    </row>
-    <row r="93" spans="1:20" s="26" customFormat="1">
+      <c r="U92" s="23"/>
+    </row>
+    <row r="93" spans="1:21" s="26" customFormat="1">
       <c r="A93" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>177</v>
+        <v>288</v>
       </c>
       <c r="C93" s="37" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="D93" s="37"/>
       <c r="E93" s="11"/>
       <c r="F93" s="6"/>
       <c r="G93" s="50"/>
       <c r="H93" s="11" t="s">
-        <v>175</v>
+        <v>287</v>
       </c>
       <c r="I93" s="11"/>
       <c r="J93" s="6" t="s">
@@ -4478,28 +4572,29 @@
       <c r="R93" s="23"/>
       <c r="S93" s="23"/>
       <c r="T93" s="23"/>
-    </row>
-    <row r="94" spans="1:20" s="26" customFormat="1" ht="31.5">
+      <c r="U93" s="23"/>
+    </row>
+    <row r="94" spans="1:21" s="26" customFormat="1" ht="31.5">
       <c r="A94" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>178</v>
+        <v>289</v>
       </c>
       <c r="C94" s="37" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="D94" s="37" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E94" s="11"/>
       <c r="F94" s="6"/>
       <c r="G94" s="50"/>
       <c r="H94" s="11" t="s">
-        <v>175</v>
+        <v>287</v>
       </c>
       <c r="I94" s="23" t="s">
-        <v>179</v>
+        <v>290</v>
       </c>
       <c r="J94" s="6" t="s">
         <v>9</v>
@@ -4516,8 +4611,9 @@
       <c r="R94" s="23"/>
       <c r="S94" s="23"/>
       <c r="T94" s="23"/>
-    </row>
-    <row r="95" spans="1:20" s="3" customFormat="1">
+      <c r="U94" s="23"/>
+    </row>
+    <row r="95" spans="1:21" s="3" customFormat="1">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="37"/>
@@ -4538,8 +4634,9 @@
       <c r="R95" s="11"/>
       <c r="S95" s="11"/>
       <c r="T95" s="11"/>
-    </row>
-    <row r="96" spans="1:20">
+      <c r="U95" s="11"/>
+    </row>
+    <row r="96" spans="1:21">
       <c r="A96" s="6" t="s">
         <v>11</v>
       </c>
@@ -4547,7 +4644,7 @@
         <v>44</v>
       </c>
       <c r="C96" s="51" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="D96" s="52"/>
       <c r="E96" s="35"/>
@@ -4566,8 +4663,9 @@
       <c r="R96" s="35"/>
       <c r="S96" s="35"/>
       <c r="T96" s="35"/>
-    </row>
-    <row r="97" spans="1:20">
+      <c r="U96" s="35"/>
+    </row>
+    <row r="97" spans="1:21">
       <c r="A97" s="6" t="s">
         <v>69</v>
       </c>
@@ -4590,8 +4688,9 @@
       <c r="R97" s="35"/>
       <c r="S97" s="35"/>
       <c r="T97" s="35"/>
-    </row>
-    <row r="98" spans="1:20">
+      <c r="U97" s="35"/>
+    </row>
+    <row r="98" spans="1:21">
       <c r="A98" s="6" t="s">
         <v>13</v>
       </c>
@@ -4616,8 +4715,9 @@
       <c r="R98" s="35"/>
       <c r="S98" s="35"/>
       <c r="T98" s="35"/>
-    </row>
-    <row r="99" spans="1:20">
+      <c r="U98" s="35"/>
+    </row>
+    <row r="99" spans="1:21">
       <c r="A99" s="34" t="s">
         <v>14</v>
       </c>
@@ -4642,6 +4742,7 @@
       <c r="R99" s="35"/>
       <c r="S99" s="35"/>
       <c r="T99" s="35"/>
+      <c r="U99" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -4671,7 +4772,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="D1" s="53" t="s">
         <v>16</v>
@@ -4689,10 +4790,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="C2" s="52" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4700,10 +4801,10 @@
         <v>18</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="C3" s="52" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4711,10 +4812,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4722,10 +4823,10 @@
         <v>27</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4733,10 +4834,10 @@
         <v>27</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4774,35 +4875,35 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="35" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="35" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="35" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4815,10 +4916,10 @@
         <v>91</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4826,10 +4927,10 @@
         <v>91</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4845,7 +4946,7 @@
         <v>112</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="D17" s="54"/>
       <c r="E17" s="9"/>
@@ -4858,7 +4959,7 @@
         <v>113</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="D18" s="54"/>
       <c r="E18" s="9"/>
@@ -4870,7 +4971,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B20" s="6">
         <v>1</v>
@@ -4881,7 +4982,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B21" s="6">
         <v>2</v>
@@ -4892,7 +4993,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B22" s="6">
         <v>3</v>
@@ -4903,7 +5004,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B23" s="6">
         <v>4</v>
@@ -4914,7 +5015,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B24" s="6">
         <v>5</v>
@@ -4925,7 +5026,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B25" s="6">
         <v>6</v>
@@ -4936,7 +5037,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B26" s="6">
         <v>7</v>
@@ -4947,7 +5048,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B27" s="6">
         <v>8</v>
@@ -4958,7 +5059,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B28" s="6">
         <v>9</v>
@@ -4969,7 +5070,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B29" s="6">
         <v>10</v>
@@ -4985,90 +5086,90 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="35" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="35" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C32" s="37" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="35" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="35" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="35" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>130</v>
+        <v>298</v>
       </c>
       <c r="C35" s="37" t="s">
-        <v>130</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="35" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="35" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C37" s="37" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="35" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>174</v>
+        <v>291</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>133</v>
+        <v>292</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -5078,13 +5179,13 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="5" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="C40" s="55" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -5115,13 +5216,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>181</v>
+        <v>280</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>116</v>
+        <v>282</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
